--- a/tinHelm/excel/7_RoleCard.xlsx
+++ b/tinHelm/excel/7_RoleCard.xlsx
@@ -348,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="3" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -473,7 +473,7 @@
         <v>70004</v>
       </c>
       <c r="B9" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C9" s="1">
         <v>20004</v>
@@ -487,13 +487,13 @@
         <v>70005</v>
       </c>
       <c r="B10" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C10" s="1">
         <v>20005</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -501,13 +501,13 @@
         <v>70006</v>
       </c>
       <c r="B11" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C11" s="1">
         <v>20006</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -515,13 +515,13 @@
         <v>70007</v>
       </c>
       <c r="B12" s="1">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C12" s="1">
         <v>20007</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -529,13 +529,13 @@
         <v>70008</v>
       </c>
       <c r="B13" s="1">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C13" s="1">
         <v>20008</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -543,13 +543,307 @@
         <v>70009</v>
       </c>
       <c r="B14" s="1">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C14" s="1">
         <v>20009</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>70010</v>
+      </c>
+      <c r="B15">
+        <v>10001</v>
+      </c>
+      <c r="C15">
+        <v>20010</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>70011</v>
+      </c>
+      <c r="B16">
+        <v>10002</v>
+      </c>
+      <c r="C16">
+        <v>20011</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>70012</v>
+      </c>
+      <c r="B17">
+        <v>10002</v>
+      </c>
+      <c r="C17">
+        <v>20012</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>70013</v>
+      </c>
+      <c r="B18">
+        <v>10002</v>
+      </c>
+      <c r="C18">
+        <v>20013</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>70014</v>
+      </c>
+      <c r="B19">
+        <v>10002</v>
+      </c>
+      <c r="C19">
+        <v>20014</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>70015</v>
+      </c>
+      <c r="B20">
+        <v>10002</v>
+      </c>
+      <c r="C20">
+        <v>20015</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>70016</v>
+      </c>
+      <c r="B21">
+        <v>10002</v>
+      </c>
+      <c r="C21">
+        <v>20016</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>70017</v>
+      </c>
+      <c r="B22">
+        <v>10002</v>
+      </c>
+      <c r="C22">
+        <v>20017</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>70018</v>
+      </c>
+      <c r="B23">
+        <v>10002</v>
+      </c>
+      <c r="C23">
+        <v>20018</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>70019</v>
+      </c>
+      <c r="B24">
+        <v>10002</v>
+      </c>
+      <c r="C24">
+        <v>20019</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>70020</v>
+      </c>
+      <c r="B25">
+        <v>10002</v>
+      </c>
+      <c r="C25">
+        <v>20020</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>70021</v>
+      </c>
+      <c r="B26">
+        <v>10003</v>
+      </c>
+      <c r="C26">
+        <v>20021</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>70022</v>
+      </c>
+      <c r="B27">
+        <v>10003</v>
+      </c>
+      <c r="C27">
+        <v>20022</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>70023</v>
+      </c>
+      <c r="B28">
+        <v>10003</v>
+      </c>
+      <c r="C28">
+        <v>20023</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>70024</v>
+      </c>
+      <c r="B29">
+        <v>10003</v>
+      </c>
+      <c r="C29">
+        <v>20024</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>70025</v>
+      </c>
+      <c r="B30">
+        <v>10003</v>
+      </c>
+      <c r="C30">
+        <v>20025</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>70026</v>
+      </c>
+      <c r="B31">
+        <v>10003</v>
+      </c>
+      <c r="C31">
+        <v>20026</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>70027</v>
+      </c>
+      <c r="B32">
+        <v>10003</v>
+      </c>
+      <c r="C32">
+        <v>20027</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>70028</v>
+      </c>
+      <c r="B33">
+        <v>10003</v>
+      </c>
+      <c r="C33">
+        <v>20028</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>70029</v>
+      </c>
+      <c r="B34">
+        <v>10003</v>
+      </c>
+      <c r="C34">
+        <v>20029</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>70030</v>
+      </c>
+      <c r="B35">
+        <v>10003</v>
+      </c>
+      <c r="C35">
+        <v>20030</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
